--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260714.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260714.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D98"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>42,584,027</t>
+          <t>42,687,027</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>65.30%</t>
+          <t>65.76%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>2,571,703</t>
+          <t>2,577,703</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>6.18%</t>
+          <t>6.01%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>21,329,000</t>
+          <t>21,380,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.21%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>5,795,267</t>
+          <t>5,809,267</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.37%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>20,374,286</t>
+          <t>20,424,286</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.96%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>508,000</t>
+          <t>509,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.61%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2,750,608</t>
+          <t>2,757,608</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>2,303,901</t>
+          <t>2,309,901</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>4,617,285</t>
+          <t>4,628,285</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1.10%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
@@ -809,19 +809,19 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>559,222</t>
+          <t>560,222</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>202607WTEN6F</t>
+          <t>202608WTEQ6F</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -836,24 +836,24 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>5,403,296</t>
+          <t>182,515</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -865,17 +865,17 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>181,515</t>
+          <t>5,416,296</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -887,39 +887,39 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>1,332,000</t>
+          <t>1,997,288</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>1,992,288</t>
+          <t>1,181,617</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -931,66 +931,66 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>1,178,617</t>
+          <t>1,335,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>12,821,134</t>
+          <t>5,287,520</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3481</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>5,274,520</t>
+          <t>12,852,134</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>3,416,000</t>
+          <t>3,425,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>853,349</t>
+          <t>855,349</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>600,600</t>
+          <t>601,600</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.36%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>1,899,321</t>
+          <t>1,904,321</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -1188,24 +1188,24 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.33%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>152,499</t>
+          <t>375,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>575,000</t>
+          <t>152,499</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>景碩</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>374,000</t>
+          <t>577,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>998,822</t>
+          <t>999,822</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>3,208,000</t>
+          <t>3,216,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.29%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>804,897</t>
+          <t>806,897</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,825,000</t>
+          <t>1,829,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>5,696,000</t>
+          <t>5,710,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>1,191,441</t>
+          <t>1,194,441</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>766,000</t>
+          <t>768,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>932,659</t>
+          <t>2,592,703</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,39 +1459,39 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>10,554,121</t>
+          <t>934,659</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>580,000</t>
+          <t>10,580,121</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,39 +1503,39 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>矽力*-KY</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>2,585,703</t>
+          <t>581,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.18%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>和碩</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>3,464,981</t>
+          <t>4,445,578</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>文曄</t>
+          <t>和碩</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>1,373,384</t>
+          <t>3,473,981</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>文曄</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>4,434,578</t>
+          <t>1,376,384</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>7,138,249</t>
+          <t>7,155,249</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,105 +1635,105 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>202608WVHFQ6F</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>495,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>226,000</t>
+          <t>2,186,107</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>773,000</t>
+          <t>227,000</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>1,180,076</t>
+          <t>496,000</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>0.11%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>2,181,107</t>
+          <t>775,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,22 +1745,22 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>4,938,956</t>
+          <t>1,183,076</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.11%</t>
         </is>
       </c>
     </row>
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>289,000</t>
+          <t>4,950,956</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>801,000</t>
+          <t>290,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,22 +1833,22 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>1,553,400</t>
+          <t>803,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>388,000</t>
+          <t>389,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,22 +1877,22 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>93,000</t>
+          <t>1,557,400</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.09%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>115,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,22 +1921,22 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>318,000</t>
+          <t>93,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>0.07%</t>
+          <t>0.08%</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>998,121</t>
+          <t>1,001,121</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>156,000</t>
+          <t>319,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>1,750,000</t>
+          <t>1,754,000</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>202607WVHFN6F</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>65,538</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>202608WVHFQ6F</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>170,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,83 +2053,83 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>采鈺</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>170,000</t>
+          <t>178,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>65,538</t>
+          <t>678,000</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>6789</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>采鈺</t>
+          <t>德律</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>177,000</t>
+          <t>254,000</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>253,000</t>
+          <t>156,000</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -2141,17 +2141,17 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>神基</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>677,000</t>
+          <t>331,000</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -2163,39 +2163,39 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>330,000</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.04%</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>71,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>334,000</t>
+          <t>335,000</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -2229,39 +2229,35 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>71,000</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>0.03%</t>
-        </is>
-      </c>
+          <t>851,530,806</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>M_NTD</t>
         </is>
       </c>
       <c r="B96" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>MARGIN</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>455,514,683</t>
+          <t>381,218,178</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr"/>
@@ -2269,38 +2265,20 @@
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
         <is>
-          <t>M_NTD</t>
+          <t>RDI_NTD</t>
         </is>
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>MARGIN</t>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>406,764,847</t>
+          <t>-395,644,694</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="inlineStr">
-        <is>
-          <t>RDI_NTD</t>
-        </is>
-      </c>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C98" s="4" t="inlineStr">
-        <is>
-          <t>-37,881,783</t>
-        </is>
-      </c>
-      <c r="D98" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
